--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261007.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261007.xlsx
@@ -5708,12 +5708,12 @@
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>2-16</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -5746,7 +5746,7 @@
         <v>-20</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M9" s="15" t="inlineStr">
         <is>
@@ -5755,7 +5755,7 @@
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>なし（当方で実施可能）</t>
+          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
         </is>
       </c>
     </row>
@@ -5767,17 +5767,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>2-16</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -5787,39 +5787,39 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H10" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H10" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I10" s="13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>20</v>
+        <v>64.5</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>-20</v>
+        <v>-4.5</v>
       </c>
       <c r="L10" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M10" s="15" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
@@ -5831,17 +5831,17 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H11" s="16" t="inlineStr">
@@ -5865,13 +5865,13 @@
         </is>
       </c>
       <c r="I11" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J11" s="13" t="n">
-        <v>64.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K11" s="13" t="n">
-        <v>-4.5</v>
+        <v>-3.6</v>
       </c>
       <c r="L11" s="5" t="n">
         <v>3</v>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -5900,17 +5900,17 @@
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -5923,9 +5923,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H12" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H12" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="I12" s="13" t="n">
@@ -5938,7 +5938,7 @@
         <v>-3.6</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
+          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
         </is>
       </c>
     </row>
@@ -5959,22 +5959,22 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
@@ -5984,25 +5984,25 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H13" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H13" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I13" s="13" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>73.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>-3.6</v>
+        <v>-1.8</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M13" s="17" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6048,25 +6048,25 @@
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H14" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H14" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I14" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J14" s="13" t="n">
-        <v>31.8</v>
+        <v>100</v>
       </c>
       <c r="K14" s="13" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M14" s="17" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
       </c>
       <c r="N14" s="6" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -6130,7 +6130,7 @@
         <v>0</v>
       </c>
       <c r="L15" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M15" s="17" t="inlineStr">
         <is>
@@ -6151,17 +6151,17 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6235,12 +6235,12 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -6284,12 +6284,12 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -6368,7 +6368,7 @@
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H19" s="17" t="inlineStr">
@@ -6407,17 +6407,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H20" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H20" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I20" s="13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K20" s="13" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
         </is>
       </c>
     </row>
@@ -6471,17 +6471,17 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -6491,24 +6491,24 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H21" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H21" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I21" s="13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J21" s="13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K21" s="13" t="n">
         <v>0</v>
@@ -6523,7 +6523,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -6540,12 +6540,12 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6560,7 +6560,7 @@
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H22" s="12" t="inlineStr">
@@ -6587,7 +6587,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
         </is>
       </c>
     </row>
@@ -6599,17 +6599,17 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6619,30 +6619,30 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H23" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H23" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I23" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J23" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K23" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M23" s="17" t="inlineStr">
         <is>
@@ -6651,7 +6651,7 @@
       </c>
       <c r="N23" s="6" t="inlineStr">
         <is>
-          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6668,12 +6668,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6683,12 +6683,12 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H24" s="17" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6747,7 +6747,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
@@ -6796,12 +6796,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -6855,17 +6855,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -6875,12 +6875,12 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H27" s="17" t="inlineStr">
@@ -6919,17 +6919,17 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -6939,24 +6939,24 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H28" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H28" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I28" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J28" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K28" s="13" t="n">
         <v>0</v>
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
@@ -6983,32 +6983,32 @@
       </c>
       <c r="B29" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -7052,12 +7052,12 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -7067,12 +7067,12 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -7111,32 +7111,32 @@
       </c>
       <c r="B31" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -7180,27 +7180,27 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -7239,17 +7239,17 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -7259,12 +7259,12 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H33" s="12" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
@@ -7303,50 +7303,50 @@
       </c>
       <c r="B34" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H34" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H34" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I34" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J34" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K34" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L34" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M34" s="17" t="inlineStr">
         <is>
@@ -7355,7 +7355,7 @@
       </c>
       <c r="N34" s="6" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7372,27 +7372,27 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H35" s="17" t="inlineStr">
@@ -7431,44 +7431,44 @@
       </c>
       <c r="B36" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H36" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I36" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J36" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K36" s="13" t="n">
         <v>0</v>
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -7500,17 +7500,17 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
@@ -7547,7 +7547,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
@@ -7559,17 +7559,17 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
@@ -7579,24 +7579,24 @@
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H38" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>0</v>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7623,44 +7623,44 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H39" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H39" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I39" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K39" s="13" t="n">
         <v>0</v>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
         </is>
       </c>
     </row>
@@ -7687,17 +7687,17 @@
       </c>
       <c r="B40" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
@@ -7707,30 +7707,30 @@
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H40" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H40" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I40" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M40" s="17" t="inlineStr">
         <is>
@@ -7739,7 +7739,7 @@
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
+          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
         </is>
       </c>
     </row>
@@ -7756,17 +7756,17 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
@@ -7776,7 +7776,7 @@
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H41" s="16" t="inlineStr">
@@ -7785,25 +7785,25 @@
         </is>
       </c>
       <c r="I41" s="13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>29.8</v>
+        <v>23.7</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>0.2</v>
+        <v>16.3</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M41" s="17" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>4</v>
+      </c>
+      <c r="M41" s="18" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
+          <t>A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認</t>
         </is>
       </c>
     </row>
@@ -7820,12 +7820,12 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -7835,7 +7835,7 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
@@ -7849,16 +7849,16 @@
         </is>
       </c>
       <c r="I42" s="13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="K42" s="13" t="n">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認</t>
+          <t>条件なしで着手できる。調査結果を待たずに構成・本文は書ける</t>
         </is>
       </c>
     </row>
@@ -7879,17 +7879,17 @@
       </c>
       <c r="B43" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -7899,12 +7899,12 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H43" s="16" t="inlineStr">
@@ -7913,16 +7913,16 @@
         </is>
       </c>
       <c r="I43" s="13" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K43" s="13" t="n">
         <v>30</v>
       </c>
       <c r="L43" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M43" s="18" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>条件なしで着手できる。調査結果を待たずに構成・本文は書ける</t>
+          <t>レビュー所見の反映（重大5件）。うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
@@ -7948,12 +7948,12 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>2-15</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>介護保険の利用の有無による問31の再集計</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -7963,24 +7963,24 @@
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H44" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H44" s="15" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="I44" s="13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K44" s="13" t="n">
         <v>30</v>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>レビュー所見の反映（重大5件）。うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>個票（1件ごとの回答データ）。集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
@@ -13321,7 +13321,7 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>障がい計画　予定進捗率 51.8％　対　実績進捗率 52.6％　乖離 +0.8ポイント　／　おおむね予定どおり 31件／前倒し 9件／期限超過（1か月） 5件／遅れ 3件／期限超過（2か月） 1件</t>
+          <t>障がい計画　予定進捗率 51.8％　対　実績進捗率 53.8％　乖離 +2.0ポイント　／　おおむね予定どおり 31件／前倒し 10件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
         </is>
       </c>
     </row>
@@ -14141,17 +14141,17 @@
     <row r="18">
       <c r="A18" s="5" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T19</t>
         </is>
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>一次資料との突合の対象を広げる</t>
+          <t>問31と給付実績の食い違いの切り分け（周辺度数まで）</t>
         </is>
       </c>
       <c r="C18" s="6" t="inlineStr">
         <is>
-          <t>原本（年報・国保連月報・交付金の集計表・総合事業ワークシート）が手元にある。現在の286件は調査結果報告書と年報が主で、月報・交付金集計表からの数値は一部しか照合していない</t>
+          <t>周辺度数（それぞれの設問の合計）だけでも、取り違え仮説が人数として成立しうるかは測れる。個票がないためクロス集計はできないが、取り違えでは説明できない分を切り出すところまでは当方で完結する</t>
         </is>
       </c>
       <c r="D18" s="5" t="n">
@@ -14159,44 +14159,44 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>check_ono_ichiji.py</t>
+          <t>23_障がいアンケート分析／食い違いの切り分け</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>障がい 2-15</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="H18" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月7日（水）</t>
+        </is>
+      </c>
+      <c r="H18" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>一次資料との突合の対象を広げる</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>T18で必要と判定した。既存データでできるため追加調査が要らない。調査の「現在利用」が給付実績と合っていない原因が、介護保険との取り違えで説明できるかを確かめる。結果によって短期入所の照会の主題が変わるため、照会より先に行う</t>
+          <t>原本（年報・国保連月報・交付金の集計表・総合事業ワークシート）が手元にある。現在の286件は調査結果報告書と年報が主で、月報・交付金集計表からの数値は一部しか照合していない</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -14204,12 +14204,12 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>問31の層別再集計</t>
+          <t>check_ono_ichiji.py</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>障がい 2-15</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
@@ -14343,7 +14343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14436,12 +14436,12 @@
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>T19</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="D3" s="6" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -14454,131 +14454,98 @@
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>障がい 2-15</t>
+          <t>障がい 2-16</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="inlineStr">
+      <c r="A4" s="20" t="inlineStr">
         <is>
           <t>10月8日（木）</t>
         </is>
       </c>
-      <c r="B4" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
+      <c r="B4" s="20" t="inlineStr"/>
+      <c r="C4" s="20" t="inlineStr"/>
+      <c r="D4" s="21" t="inlineStr">
+        <is>
+          <t>── 10月8日（木） 計</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="n">
+        <v>4</v>
+      </c>
+      <c r="F4" s="20" t="inlineStr">
+        <is>
+          <t>残4.0h</t>
+        </is>
+      </c>
+      <c r="G4" s="20" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="inlineStr">
+        <is>
+          <t>10月9日（金）</t>
+        </is>
+      </c>
+      <c r="B5" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画の素案の改訂（第2版）</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F5" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>障がい 2-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>── 10月8日（木） 計</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
+      <c r="G5" s="5" t="inlineStr">
+        <is>
+          <t>障がい 3-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr">
+        <is>
+          <t>10月9日（金）</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr"/>
+      <c r="C6" s="20" t="inlineStr"/>
+      <c r="D6" s="21" t="inlineStr">
+        <is>
+          <t>── 10月9日（金） 計</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="20" t="inlineStr">
+      <c r="F6" s="20" t="inlineStr">
         <is>
           <t>残6.0h</t>
         </is>
       </c>
-      <c r="G5" s="20" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="5" t="inlineStr">
-        <is>
-          <t>10月9日（金）</t>
-        </is>
-      </c>
-      <c r="B6" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="D6" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画の素案の改訂（第2版）</t>
-        </is>
-      </c>
-      <c r="E6" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G6" s="5" t="inlineStr">
-        <is>
-          <t>障がい 3-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="20" t="inlineStr">
-        <is>
-          <t>10月9日（金）</t>
-        </is>
-      </c>
-      <c r="B7" s="20" t="inlineStr"/>
-      <c r="C7" s="20" t="inlineStr"/>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>── 10月9日（金） 計</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F7" s="20" t="inlineStr">
-        <is>
-          <t>残6.0h</t>
-        </is>
-      </c>
-      <c r="G7" s="20" t="inlineStr"/>
+      <c r="G6" s="20" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="11" t="inlineStr">
+        <is>
+          <t>※ 10月8日（木）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>※ 10月8日（木）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261007.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261007.xlsx
@@ -5703,17 +5703,17 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>2-16</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="D9" s="6" t="inlineStr">
         <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
+          <t>骨子案の作成</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -5723,39 +5723,39 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H9" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H9" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I9" s="13" t="n">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="J9" s="13" t="n">
-        <v>20</v>
+        <v>64.5</v>
       </c>
       <c r="K9" s="13" t="n">
-        <v>-20</v>
+        <v>-4.5</v>
       </c>
       <c r="L9" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="M9" s="15" t="inlineStr">
-        <is>
-          <t>遅れ</t>
+        <v>3</v>
+      </c>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>おおむね予定どおり</t>
         </is>
       </c>
       <c r="N9" s="6" t="inlineStr">
         <is>
-          <t>2-15の結果（短期入所の照会の主題が変わる）</t>
+          <t>調査結果の反映</t>
         </is>
       </c>
     </row>
@@ -5767,17 +5767,17 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>6-1</t>
+          <t>5-1</t>
         </is>
       </c>
       <c r="D10" s="6" t="inlineStr">
         <is>
-          <t>骨子案の作成</t>
+          <t>現行計画の取組み状況の検証</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -5787,12 +5787,12 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="H10" s="16" t="inlineStr">
@@ -5801,13 +5801,13 @@
         </is>
       </c>
       <c r="I10" s="13" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J10" s="13" t="n">
-        <v>64.5</v>
+        <v>73.59999999999999</v>
       </c>
       <c r="K10" s="13" t="n">
-        <v>-4.5</v>
+        <v>-3.6</v>
       </c>
       <c r="L10" s="5" t="n">
         <v>3</v>
@@ -5819,7 +5819,7 @@
       </c>
       <c r="N10" s="6" t="inlineStr">
         <is>
-          <t>調査結果の反映</t>
+          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
         </is>
       </c>
     </row>
@@ -5836,17 +5836,17 @@
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>5-1</t>
+          <t>5-4</t>
         </is>
       </c>
       <c r="D11" s="6" t="inlineStr">
         <is>
-          <t>現行計画の取組み状況の検証</t>
+          <t>人口推計の出典の統一</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
@@ -5859,9 +5859,9 @@
           <t>2026-10</t>
         </is>
       </c>
-      <c r="H11" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H11" s="14" t="inlineStr">
+        <is>
+          <t>要対応</t>
         </is>
       </c>
       <c r="I11" s="13" t="n">
@@ -5874,7 +5874,7 @@
         <v>-3.6</v>
       </c>
       <c r="L11" s="5" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M11" s="17" t="inlineStr">
         <is>
@@ -5883,7 +5883,7 @@
       </c>
       <c r="N11" s="6" t="inlineStr">
         <is>
-          <t>前回計画31項目の令和8年度末の実績（依頼票D6）。目標値は受領済みのため、残るのは実績のみ</t>
+          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
         </is>
       </c>
     </row>
@@ -5895,22 +5895,22 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>5-4</t>
+          <t>7-4</t>
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr">
         <is>
-          <t>人口推計の出典の統一</t>
+          <t>自立支援協議会への出席（3回）</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
@@ -5920,25 +5920,25 @@
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H12" s="14" t="inlineStr">
-        <is>
-          <t>要対応</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H12" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I12" s="13" t="n">
-        <v>70</v>
+        <v>30</v>
       </c>
       <c r="J12" s="13" t="n">
-        <v>73.59999999999999</v>
+        <v>31.8</v>
       </c>
       <c r="K12" s="13" t="n">
-        <v>-3.6</v>
+        <v>-1.8</v>
       </c>
       <c r="L12" s="5" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M12" s="17" t="inlineStr">
         <is>
@@ -5947,7 +5947,7 @@
       </c>
       <c r="N12" s="6" t="inlineStr">
         <is>
-          <t>町の判断（4件）。計画本文の出典、男女別5歳階級の住基人口の提供、障がい児の見込量を再計算するか、保険料算定に第10期推計を使うこと</t>
+          <t>第2回・第3回の時期は工程変更の協議による</t>
         </is>
       </c>
     </row>
@@ -5959,17 +5959,17 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>7-4</t>
+          <t>2-3</t>
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr">
         <is>
-          <t>自立支援協議会への出席（3回）</t>
+          <t>調査票の作成と補修正</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -5984,25 +5984,25 @@
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
-        </is>
-      </c>
-      <c r="H13" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H13" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I13" s="13" t="n">
-        <v>30</v>
+        <v>100</v>
       </c>
       <c r="J13" s="13" t="n">
-        <v>31.8</v>
+        <v>100</v>
       </c>
       <c r="K13" s="13" t="n">
-        <v>-1.8</v>
+        <v>0</v>
       </c>
       <c r="L13" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M13" s="17" t="inlineStr">
         <is>
@@ -6011,7 +6011,7 @@
       </c>
       <c r="N13" s="6" t="inlineStr">
         <is>
-          <t>第2回・第3回の時期は工程変更の協議による</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6023,17 +6023,17 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>2-3</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="D14" s="6" t="inlineStr">
         <is>
-          <t>調査票の作成と補修正</t>
+          <t>委託仕様書の確認と適合性チェック</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -6066,7 +6066,7 @@
         <v>0</v>
       </c>
       <c r="L14" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M14" s="17" t="inlineStr">
         <is>
@@ -6087,17 +6087,17 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>2-1</t>
         </is>
       </c>
       <c r="D15" s="6" t="inlineStr">
         <is>
-          <t>委託仕様書の確認と適合性チェック</t>
+          <t>調査内容の企画</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -6107,12 +6107,12 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="H15" s="17" t="inlineStr">
@@ -6156,12 +6156,12 @@
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>2-1</t>
+          <t>2-2</t>
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr">
         <is>
-          <t>調査内容の企画</t>
+          <t>調査実施設計</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H16" s="17" t="inlineStr">
@@ -6220,12 +6220,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>2-2</t>
+          <t>2-8</t>
         </is>
       </c>
       <c r="D17" s="6" t="inlineStr">
         <is>
-          <t>調査実施設計</t>
+          <t>調査の発送・回収</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -6240,7 +6240,7 @@
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H17" s="17" t="inlineStr">
@@ -6279,17 +6279,17 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>2-8</t>
+          <t>3-1</t>
         </is>
       </c>
       <c r="D18" s="6" t="inlineStr">
         <is>
-          <t>調査の発送・回収</t>
+          <t>実施計画と質問票の作成</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -6304,7 +6304,7 @@
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H18" s="17" t="inlineStr">
@@ -6343,17 +6343,17 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>3-1</t>
+          <t>5-2</t>
         </is>
       </c>
       <c r="D19" s="6" t="inlineStr">
         <is>
-          <t>実施計画と質問票の作成</t>
+          <t>手帳所持者・サービス利用状況の分析</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -6363,24 +6363,24 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H19" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H19" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I19" s="13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="J19" s="13" t="n">
-        <v>100</v>
+        <v>60</v>
       </c>
       <c r="K19" s="13" t="n">
         <v>0</v>
@@ -6395,7 +6395,7 @@
       </c>
       <c r="N19" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
         </is>
       </c>
     </row>
@@ -6407,17 +6407,17 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>5-2</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="D20" s="6" t="inlineStr">
         <is>
-          <t>手帳所持者・サービス利用状況の分析</t>
+          <t>計画案の作成</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -6427,24 +6427,24 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H20" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2027-02</t>
+        </is>
+      </c>
+      <c r="H20" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I20" s="13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="J20" s="13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K20" s="13" t="n">
         <v>0</v>
@@ -6459,7 +6459,7 @@
       </c>
       <c r="N20" s="6" t="inlineStr">
         <is>
-          <t>支給決定量と実利用量の別、障害支援区分別の状況（依頼票D7）。精神障がい者の内数が総数を超える箇所があり原データの確認が必要</t>
+          <t>意見への対応</t>
         </is>
       </c>
     </row>
@@ -6476,12 +6476,12 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>8-1</t>
+          <t>8-2</t>
         </is>
       </c>
       <c r="D21" s="6" t="inlineStr">
         <is>
-          <t>計画案の作成</t>
+          <t>レイアウトデザイン・イラスト起こし</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -6523,7 +6523,7 @@
       </c>
       <c r="N21" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
         </is>
       </c>
     </row>
@@ -6535,17 +6535,17 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P1 準備・現状把握</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>8-2</t>
+          <t>1-1</t>
         </is>
       </c>
       <c r="D22" s="6" t="inlineStr">
         <is>
-          <t>レイアウトデザイン・イラスト起こし</t>
+          <t>契約・体制の確立、キックオフ</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -6555,30 +6555,30 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2026-06</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H22" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-07</t>
+        </is>
+      </c>
+      <c r="H22" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I22" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J22" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K22" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M22" s="17" t="inlineStr">
         <is>
@@ -6587,7 +6587,7 @@
       </c>
       <c r="N22" s="6" t="inlineStr">
         <is>
-          <t>イラスト起こしが仕様に含まれる点は引継ぎ資料でも触れられていない。デザイン工程の確保が必要</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -6604,12 +6604,12 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>1-3</t>
         </is>
       </c>
       <c r="D23" s="6" t="inlineStr">
         <is>
-          <t>契約・体制の確立、キックオフ</t>
+          <t>現行計画（第7期・第3期）の確認</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>2026-06</t>
+          <t>2026-07</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="H23" s="17" t="inlineStr">
@@ -6668,12 +6668,12 @@
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>1-3</t>
+          <t>1-4</t>
         </is>
       </c>
       <c r="D24" s="6" t="inlineStr">
         <is>
-          <t>現行計画（第7期・第3期）の確認</t>
+          <t>第3期地域福祉計画との役割分担の整理</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -6683,7 +6683,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>2026-07</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
@@ -6732,12 +6732,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>1-4</t>
+          <t>1-5</t>
         </is>
       </c>
       <c r="D25" s="6" t="inlineStr">
         <is>
-          <t>第3期地域福祉計画との役割分担の整理</t>
+          <t>町への資料依頼票の作成</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -6791,17 +6791,17 @@
       </c>
       <c r="B26" s="6" t="inlineStr">
         <is>
-          <t>P1 準備・現状把握</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>1-5</t>
+          <t>2-6</t>
         </is>
       </c>
       <c r="D26" s="6" t="inlineStr">
         <is>
-          <t>町への資料依頼票の作成</t>
+          <t>調査用品の準備・印刷</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -6811,12 +6811,12 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H26" s="17" t="inlineStr">
@@ -6855,17 +6855,17 @@
       </c>
       <c r="B27" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P3 ヒアリング</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>2-6</t>
+          <t>3-5</t>
         </is>
       </c>
       <c r="D27" s="6" t="inlineStr">
         <is>
-          <t>調査用品の準備・印刷</t>
+          <t>記録の作成と対象先への確認</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -6875,24 +6875,24 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H27" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H27" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I27" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J27" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K27" s="13" t="n">
         <v>0</v>
@@ -6907,7 +6907,7 @@
       </c>
       <c r="N27" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>ヒアリングの実施</t>
         </is>
       </c>
     </row>
@@ -6919,32 +6919,32 @@
       </c>
       <c r="B28" s="6" t="inlineStr">
         <is>
-          <t>P3 ヒアリング</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>3-5</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="D28" s="6" t="inlineStr">
         <is>
-          <t>記録の作成と対象先への確認</t>
+          <t>骨子案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="H28" s="12" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="N28" s="6" t="inlineStr">
         <is>
-          <t>ヒアリングの実施</t>
+          <t>工程変更の合意</t>
         </is>
       </c>
     </row>
@@ -6988,12 +6988,12 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-6</t>
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr">
         <is>
-          <t>骨子案の協議（自立支援協議会）</t>
+          <t>素案の協議（自立支援協議会）</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -7003,12 +7003,12 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H29" s="12" t="inlineStr">
@@ -7035,7 +7035,7 @@
       </c>
       <c r="N29" s="6" t="inlineStr">
         <is>
-          <t>工程変更の合意</t>
+          <t>素案の確定</t>
         </is>
       </c>
     </row>
@@ -7047,32 +7047,32 @@
       </c>
       <c r="B30" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>6-6</t>
+          <t>7-2</t>
         </is>
       </c>
       <c r="D30" s="6" t="inlineStr">
         <is>
-          <t>素案の協議（自立支援協議会）</t>
+          <t>パブリックコメントの実施</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H30" s="12" t="inlineStr">
@@ -7099,7 +7099,7 @@
       </c>
       <c r="N30" s="6" t="inlineStr">
         <is>
-          <t>素案の確定</t>
+          <t>素案の確定、実施時期の確定（依頼票C6）</t>
         </is>
       </c>
     </row>
@@ -7116,27 +7116,27 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>7-2</t>
+          <t>7-3</t>
         </is>
       </c>
       <c r="D31" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの実施</t>
+          <t>意見への対応</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H31" s="12" t="inlineStr">
@@ -7163,7 +7163,7 @@
       </c>
       <c r="N31" s="6" t="inlineStr">
         <is>
-          <t>素案の確定、実施時期の確定（依頼票C6）</t>
+          <t>パブコメの実施</t>
         </is>
       </c>
     </row>
@@ -7175,17 +7175,17 @@
       </c>
       <c r="B32" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>7-3</t>
+          <t>8-3</t>
         </is>
       </c>
       <c r="D32" s="6" t="inlineStr">
         <is>
-          <t>意見への対応</t>
+          <t>リライト作業</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H32" s="12" t="inlineStr">
@@ -7227,7 +7227,7 @@
       </c>
       <c r="N32" s="6" t="inlineStr">
         <is>
-          <t>パブコメの実施</t>
+          <t>計画案の確定</t>
         </is>
       </c>
     </row>
@@ -7239,50 +7239,50 @@
       </c>
       <c r="B33" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>8-3</t>
+          <t>2-4</t>
         </is>
       </c>
       <c r="D33" s="6" t="inlineStr">
         <is>
-          <t>リライト作業</t>
+          <t>調査票原案の町の確認</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H33" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H33" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I33" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J33" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K33" s="13" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M33" s="17" t="inlineStr">
         <is>
@@ -7291,7 +7291,7 @@
       </c>
       <c r="N33" s="6" t="inlineStr">
         <is>
-          <t>計画案の確定</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7308,27 +7308,27 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>2-4</t>
+          <t>2-7</t>
         </is>
       </c>
       <c r="D34" s="6" t="inlineStr">
         <is>
-          <t>調査票原案の町の確認</t>
+          <t>宛名ラベルの作成</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="H34" s="17" t="inlineStr">
@@ -7367,44 +7367,44 @@
       </c>
       <c r="B35" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>2-7</t>
+          <t>4-2</t>
         </is>
       </c>
       <c r="D35" s="6" t="inlineStr">
         <is>
-          <t>宛名ラベルの作成</t>
+          <t>町による報告書の確認</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>町</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
-        </is>
-      </c>
-      <c r="H35" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H35" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I35" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J35" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K35" s="13" t="n">
         <v>0</v>
@@ -7419,7 +7419,7 @@
       </c>
       <c r="N35" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>報告書の作成</t>
         </is>
       </c>
     </row>
@@ -7436,17 +7436,17 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>4-2</t>
+          <t>4-3</t>
         </is>
       </c>
       <c r="D36" s="6" t="inlineStr">
         <is>
-          <t>町による報告書の確認</t>
+          <t>報告書の完成・納品</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
         <is>
-          <t>町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="N36" s="6" t="inlineStr">
         <is>
-          <t>報告書の作成</t>
+          <t>町の確認</t>
         </is>
       </c>
     </row>
@@ -7495,17 +7495,17 @@
       </c>
       <c r="B37" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P7 意見聴取</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>4-3</t>
+          <t>7-1</t>
         </is>
       </c>
       <c r="D37" s="6" t="inlineStr">
         <is>
-          <t>報告書の完成・納品</t>
+          <t>パブリックコメントの様式作成</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -7515,24 +7515,24 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-08</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H37" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-08</t>
+        </is>
+      </c>
+      <c r="H37" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I37" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="J37" s="13" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="K37" s="13" t="n">
         <v>0</v>
@@ -7547,7 +7547,7 @@
       </c>
       <c r="N37" s="6" t="inlineStr">
         <is>
-          <t>町の確認</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -7559,44 +7559,44 @@
       </c>
       <c r="B38" s="6" t="inlineStr">
         <is>
-          <t>P7 意見聴取</t>
+          <t>P8 完成・納品</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>7-1</t>
+          <t>8-4</t>
         </is>
       </c>
       <c r="D38" s="6" t="inlineStr">
         <is>
-          <t>パブリックコメントの様式作成</t>
+          <t>納品・検収</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr">
         <is>
-          <t>受託者</t>
+          <t>受託者・町</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>2026-08</t>
-        </is>
-      </c>
-      <c r="H38" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2027-03</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>未着手</t>
         </is>
       </c>
       <c r="I38" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="J38" s="13" t="n">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="K38" s="13" t="n">
         <v>0</v>
@@ -7611,7 +7611,7 @@
       </c>
       <c r="N38" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
         </is>
       </c>
     </row>
@@ -7623,17 +7623,17 @@
       </c>
       <c r="B39" s="6" t="inlineStr">
         <is>
-          <t>P8 完成・納品</t>
+          <t>P6 計画策定支援</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>8-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="D39" s="6" t="inlineStr">
         <is>
-          <t>納品・検収</t>
+          <t>成果目標の設定</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -7643,30 +7643,30 @@
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
-        </is>
-      </c>
-      <c r="H39" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H39" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I39" s="13" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="J39" s="13" t="n">
-        <v>0</v>
+        <v>29.8</v>
       </c>
       <c r="K39" s="13" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="L39" s="5" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M39" s="17" t="inlineStr">
         <is>
@@ -7675,7 +7675,7 @@
       </c>
       <c r="N39" s="6" t="inlineStr">
         <is>
-          <t>完了日が公告（3月31日）と仕様書（3月25日）で異なる（依頼票C1）</t>
+          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
         </is>
       </c>
     </row>
@@ -7692,17 +7692,17 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="D40" s="6" t="inlineStr">
         <is>
-          <t>成果目標の設定</t>
+          <t>サービス見込量の算定</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
         <is>
-          <t>受託者・町</t>
+          <t>受託者</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
@@ -7712,7 +7712,7 @@
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2027-01</t>
         </is>
       </c>
       <c r="H40" s="16" t="inlineStr">
@@ -7721,25 +7721,25 @@
         </is>
       </c>
       <c r="I40" s="13" t="n">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="J40" s="13" t="n">
-        <v>29.8</v>
+        <v>23.7</v>
       </c>
       <c r="K40" s="13" t="n">
-        <v>0.2</v>
+        <v>16.3</v>
       </c>
       <c r="L40" s="5" t="n">
-        <v>3</v>
-      </c>
-      <c r="M40" s="17" t="inlineStr">
-        <is>
-          <t>おおむね予定どおり</t>
+        <v>4</v>
+      </c>
+      <c r="M40" s="18" t="inlineStr">
+        <is>
+          <t>前倒し</t>
         </is>
       </c>
       <c r="N40" s="6" t="inlineStr">
         <is>
-          <t>基準年度の確定（告示本文・県方針）、R6年度の一般就労移行者数、セルフプラン件数（依頼票D5）、特別支援学校卒業予定者（依頼票D6）</t>
+          <t>A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認</t>
         </is>
       </c>
     </row>
@@ -7756,12 +7756,12 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-5</t>
         </is>
       </c>
       <c r="D41" s="6" t="inlineStr">
         <is>
-          <t>サービス見込量の算定</t>
+          <t>素案の作成</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr">
@@ -7771,7 +7771,7 @@
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-12</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
@@ -7785,16 +7785,16 @@
         </is>
       </c>
       <c r="I41" s="13" t="n">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="J41" s="13" t="n">
-        <v>23.7</v>
+        <v>0</v>
       </c>
       <c r="K41" s="13" t="n">
-        <v>16.3</v>
+        <v>30</v>
       </c>
       <c r="L41" s="5" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="M41" s="18" t="inlineStr">
         <is>
@@ -7803,7 +7803,7 @@
       </c>
       <c r="N41" s="6" t="inlineStr">
         <is>
-          <t>A-1〜A-5の解消。とくに地域生活支援事業のR6〜R8実績（法定記載事項）と、居宅介護R7の113時間が実績か入力誤りかの確認</t>
+          <t>条件なしで着手できる。調査結果を待たずに構成・本文は書ける</t>
         </is>
       </c>
     </row>
@@ -7815,17 +7815,17 @@
       </c>
       <c r="B42" s="6" t="inlineStr">
         <is>
-          <t>P6 計画策定支援</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>6-5</t>
+          <t>2-11</t>
         </is>
       </c>
       <c r="D42" s="6" t="inlineStr">
         <is>
-          <t>素案の作成</t>
+          <t>集計・分析</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>2026-12</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>2027-01</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="H42" s="16" t="inlineStr">
@@ -7849,16 +7849,16 @@
         </is>
       </c>
       <c r="I42" s="13" t="n">
-        <v>30</v>
+        <v>70</v>
       </c>
       <c r="J42" s="13" t="n">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="K42" s="13" t="n">
         <v>30</v>
       </c>
       <c r="L42" s="5" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="M42" s="18" t="inlineStr">
         <is>
@@ -7867,7 +7867,7 @@
       </c>
       <c r="N42" s="6" t="inlineStr">
         <is>
-          <t>条件なしで着手できる。調査結果を待たずに構成・本文は書ける</t>
+          <t>レビュー所見の反映（重大5件）。うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
         </is>
       </c>
     </row>
@@ -7884,12 +7884,12 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>2-11</t>
+          <t>2-15</t>
         </is>
       </c>
       <c r="D43" s="6" t="inlineStr">
         <is>
-          <t>集計・分析</t>
+          <t>介護保険の利用の有無による問31の再集計</t>
         </is>
       </c>
       <c r="E43" s="5" t="inlineStr">
@@ -7899,24 +7899,24 @@
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H43" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H43" s="15" t="inlineStr">
+        <is>
+          <t>データ待ち</t>
         </is>
       </c>
       <c r="I43" s="13" t="n">
-        <v>70</v>
+        <v>50</v>
       </c>
       <c r="J43" s="13" t="n">
-        <v>40</v>
+        <v>20</v>
       </c>
       <c r="K43" s="13" t="n">
         <v>30</v>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="N43" s="6" t="inlineStr">
         <is>
-          <t>レビュー所見の反映（重大5件）。うち障がい児の災害設問（問41・問42）は原票の確認が要る</t>
+          <t>個票（1件ごとの回答データ）。集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
         </is>
       </c>
     </row>
@@ -7943,17 +7943,17 @@
       </c>
       <c r="B44" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P4 成果品①</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>2-15</t>
+          <t>4-1</t>
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr">
         <is>
-          <t>介護保険の利用の有無による問31の再集計</t>
+          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
         </is>
       </c>
       <c r="E44" s="5" t="inlineStr">
@@ -7968,25 +7968,25 @@
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H44" s="15" t="inlineStr">
-        <is>
-          <t>データ待ち</t>
+          <t>2026-12</t>
+        </is>
+      </c>
+      <c r="H44" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I44" s="13" t="n">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="J44" s="13" t="n">
-        <v>20</v>
+        <v>6.6</v>
       </c>
       <c r="K44" s="13" t="n">
-        <v>30</v>
+        <v>33.4</v>
       </c>
       <c r="L44" s="5" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="M44" s="18" t="inlineStr">
         <is>
@@ -7995,7 +7995,7 @@
       </c>
       <c r="N44" s="6" t="inlineStr">
         <is>
-          <t>個票（1件ごとの回答データ）。集計表は集計結果だけで個票がなく、問29×問31のクロス集計が作れない（依頼票D7）</t>
+          <t>レビュー所見の反映（重大5件）、ヒアリング記録の完成</t>
         </is>
       </c>
     </row>
@@ -8007,17 +8007,17 @@
       </c>
       <c r="B45" s="6" t="inlineStr">
         <is>
-          <t>P4 成果品①</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>4-1</t>
+          <t>2-10</t>
         </is>
       </c>
       <c r="D45" s="6" t="inlineStr">
         <is>
-          <t>アンケート調査結果及びヒアリング調査結果報告書の作成</t>
+          <t>回収票の点検・ナンバリング・データ入力</t>
         </is>
       </c>
       <c r="E45" s="5" t="inlineStr">
@@ -8027,30 +8027,30 @@
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
+          <t>2026-09</t>
+        </is>
+      </c>
+      <c r="G45" s="5" t="inlineStr">
+        <is>
           <t>2026-10</t>
         </is>
       </c>
-      <c r="G45" s="5" t="inlineStr">
-        <is>
-          <t>2026-12</t>
-        </is>
-      </c>
-      <c r="H45" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+      <c r="H45" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I45" s="13" t="n">
+        <v>100</v>
+      </c>
+      <c r="J45" s="13" t="n">
+        <v>60</v>
+      </c>
+      <c r="K45" s="13" t="n">
         <v>40</v>
       </c>
-      <c r="J45" s="13" t="n">
-        <v>6.6</v>
-      </c>
-      <c r="K45" s="13" t="n">
-        <v>33.4</v>
-      </c>
       <c r="L45" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M45" s="18" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
       </c>
       <c r="N45" s="6" t="inlineStr">
         <is>
-          <t>レビュー所見の反映（重大5件）、ヒアリング記録の完成</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -8071,17 +8071,17 @@
       </c>
       <c r="B46" s="6" t="inlineStr">
         <is>
-          <t>P2 ニーズ調査</t>
+          <t>P5 現状分析・課題</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>2-10</t>
+          <t>5-3</t>
         </is>
       </c>
       <c r="D46" s="6" t="inlineStr">
         <is>
-          <t>回収票の点検・ナンバリング・データ入力</t>
+          <t>課題の抽出</t>
         </is>
       </c>
       <c r="E46" s="5" t="inlineStr">
@@ -8091,24 +8091,24 @@
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-11</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
-        </is>
-      </c>
-      <c r="H46" s="17" t="inlineStr">
-        <is>
-          <t>完了</t>
+          <t>2026-11</t>
+        </is>
+      </c>
+      <c r="H46" s="16" t="inlineStr">
+        <is>
+          <t>進行中</t>
         </is>
       </c>
       <c r="I46" s="13" t="n">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="J46" s="13" t="n">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="K46" s="13" t="n">
         <v>40</v>
@@ -8123,7 +8123,7 @@
       </c>
       <c r="N46" s="6" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>調査結果・ヒアリング結果</t>
         </is>
       </c>
     </row>
@@ -8135,17 +8135,17 @@
       </c>
       <c r="B47" s="6" t="inlineStr">
         <is>
-          <t>P5 現状分析・課題</t>
+          <t>P2 ニーズ調査</t>
         </is>
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>5-3</t>
+          <t>2-12</t>
         </is>
       </c>
       <c r="D47" s="6" t="inlineStr">
         <is>
-          <t>課題の抽出</t>
+          <t>分析報告書のレビュー</t>
         </is>
       </c>
       <c r="E47" s="5" t="inlineStr">
@@ -8155,27 +8155,27 @@
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>2026-11</t>
-        </is>
-      </c>
-      <c r="H47" s="16" t="inlineStr">
-        <is>
-          <t>進行中</t>
+          <t>2026-10</t>
+        </is>
+      </c>
+      <c r="H47" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I47" s="13" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J47" s="13" t="n">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="K47" s="13" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="L47" s="5" t="n">
         <v>3</v>
@@ -8187,7 +8187,7 @@
       </c>
       <c r="N47" s="6" t="inlineStr">
         <is>
-          <t>調査結果・ヒアリング結果</t>
+          <t>―</t>
         </is>
       </c>
     </row>
@@ -8204,12 +8204,12 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>2-12</t>
+          <t>2-13</t>
         </is>
       </c>
       <c r="D48" s="6" t="inlineStr">
         <is>
-          <t>分析報告書のレビュー</t>
+          <t>目標値とアンケート設問の対応（MECEチェック）</t>
         </is>
       </c>
       <c r="E48" s="5" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>2-13</t>
+          <t>2-14</t>
         </is>
       </c>
       <c r="D49" s="6" t="inlineStr">
         <is>
-          <t>目標値とアンケート設問の対応（MECEチェック）</t>
+          <t>アンケートで不足する事項の洗い出しと対応方針</t>
         </is>
       </c>
       <c r="E49" s="5" t="inlineStr">
@@ -8332,12 +8332,12 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>2-14</t>
+          <t>2-16</t>
         </is>
       </c>
       <c r="D50" s="6" t="inlineStr">
         <is>
-          <t>アンケートで不足する事項の洗い出しと対応方針</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="E50" s="5" t="inlineStr">
@@ -8370,7 +8370,7 @@
         <v>80</v>
       </c>
       <c r="L50" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M50" s="18" t="inlineStr">
         <is>
@@ -13321,7 +13321,7 @@
     <row r="130">
       <c r="A130" s="19" t="inlineStr">
         <is>
-          <t>障がい計画　予定進捗率 51.8％　対　実績進捗率 53.8％　乖離 +2.0ポイント　／　おおむね予定どおり 31件／前倒し 10件／期限超過（1か月） 5件／遅れ 2件／期限超過（2か月） 1件</t>
+          <t>障がい計画　予定進捗率 51.8％　対　実績進捗率 55.5％　乖離 +3.7ポイント　／　おおむね予定どおり 31件／前倒し 11件／期限超過（1か月） 5件／期限超過（2か月） 1件／遅れ 1件</t>
         </is>
       </c>
     </row>
@@ -14186,17 +14186,17 @@
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T20</t>
         </is>
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>一次資料との突合の対象を広げる</t>
+          <t>確認票の2枚化（町向け・事業所向け）</t>
         </is>
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>原本（年報・国保連月報・交付金の集計表・総合事業ワークシート）が手元にある。現在の286件は調査結果報告書と年報が主で、月報・交付金集計表からの数値は一部しか照合していない</t>
+          <t>受領した確認票を土台にする。1枚のまま回すと回答者が担当外の行まで見ることになる。庁内で取れるものと事業所に照会するものは本書で仕分け済み</t>
         </is>
       </c>
       <c r="D19" s="5" t="n">
@@ -14204,44 +14204,44 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>check_ono_ichiji.py</t>
+          <t>確認依頼票（町）・照会票（事業所・関係機関）</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>障がい 2-16</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="H19" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月7日（水）</t>
+        </is>
+      </c>
+      <c r="H19" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>T20</t>
+          <t>T14</t>
         </is>
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
+          <t>一次資料との突合の対象を広げる</t>
         </is>
       </c>
       <c r="C20" s="6" t="inlineStr">
         <is>
-          <t>受領した確認票を土台にする。1枚のまま回すと回答者が担当外の行まで見ることになる。庁内で取れるものと事業所に照会するものは本書で仕分け済み</t>
+          <t>原本（年報・国保連月報・交付金の集計表・総合事業ワークシート）が手元にある。現在の286件は調査結果報告書と年報が主で、月報・交付金集計表からの数値は一部しか照合していない</t>
         </is>
       </c>
       <c r="D20" s="5" t="n">
@@ -14249,12 +14249,12 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>確認票（町向け・事業所向け）</t>
+          <t>check_ono_ichiji.py</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>障がい 2-16</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
@@ -14343,7 +14343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G9"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14426,126 +14426,93 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="inlineStr">
+      <c r="A3" s="20" t="inlineStr">
         <is>
           <t>10月8日（木）</t>
         </is>
       </c>
-      <c r="B3" s="5" t="n">
+      <c r="B3" s="20" t="inlineStr"/>
+      <c r="C3" s="20" t="inlineStr"/>
+      <c r="D3" s="21" t="inlineStr">
+        <is>
+          <t>── 10月8日（木） 計</t>
+        </is>
+      </c>
+      <c r="E3" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="C3" s="5" t="inlineStr">
-        <is>
-          <t>T20</t>
-        </is>
-      </c>
-      <c r="D3" s="6" t="inlineStr">
-        <is>
-          <t>確認票の2枚化（町向け・事業所向け）</t>
-        </is>
-      </c>
-      <c r="E3" s="5" t="n">
-        <v>2</v>
-      </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="20" t="inlineStr">
+        <is>
+          <t>残2.0h</t>
+        </is>
+      </c>
+      <c r="G3" s="20" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>10月9日（金）</t>
+        </is>
+      </c>
+      <c r="B4" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>T12</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>障がい計画の素案の改訂（第2版）</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="F4" s="12" t="inlineStr">
         <is>
           <t>未着手</t>
         </is>
       </c>
-      <c r="G3" s="5" t="inlineStr">
-        <is>
-          <t>障がい 2-16</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="B4" s="20" t="inlineStr"/>
-      <c r="C4" s="20" t="inlineStr"/>
-      <c r="D4" s="21" t="inlineStr">
-        <is>
-          <t>── 10月8日（木） 計</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n">
-        <v>4</v>
-      </c>
-      <c r="F4" s="20" t="inlineStr">
-        <is>
-          <t>残4.0h</t>
-        </is>
-      </c>
-      <c r="G4" s="20" t="inlineStr"/>
+      <c r="G4" s="5" t="inlineStr">
+        <is>
+          <t>障がい 3-2</t>
+        </is>
+      </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="inlineStr">
+      <c r="A5" s="20" t="inlineStr">
         <is>
           <t>10月9日（金）</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="D5" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画の素案の改訂（第2版）</t>
-        </is>
-      </c>
-      <c r="E5" s="5" t="n">
+      <c r="B5" s="20" t="inlineStr"/>
+      <c r="C5" s="20" t="inlineStr"/>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>── 10月9日（金） 計</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n">
         <v>6</v>
       </c>
-      <c r="F5" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G5" s="5" t="inlineStr">
-        <is>
-          <t>障がい 3-2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="20" t="inlineStr">
-        <is>
-          <t>10月9日（金）</t>
-        </is>
-      </c>
-      <c r="B6" s="20" t="inlineStr"/>
-      <c r="C6" s="20" t="inlineStr"/>
-      <c r="D6" s="21" t="inlineStr">
-        <is>
-          <t>── 10月9日（金） 計</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F6" s="20" t="inlineStr">
+      <c r="F5" s="20" t="inlineStr">
         <is>
           <t>残6.0h</t>
         </is>
       </c>
-      <c r="G6" s="20" t="inlineStr"/>
+      <c r="G5" s="20" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>※ 10月8日（木）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="11" t="inlineStr">
-        <is>
-          <t>※ 10月8日（木）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>

--- a/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261007.xlsx
+++ b/小野町_引継ぎ_整理済/17_業務進捗管理/小野町_ペンディング整理と作業順位_20261007.xlsx
@@ -12876,12 +12876,12 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>11-2</t>
         </is>
       </c>
       <c r="D121" s="6" t="inlineStr">
         <is>
-          <t>一次資料との全件突合</t>
+          <t>図表データ管理台帳の整備と運用</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr">
@@ -12914,7 +12914,7 @@
         <v>65</v>
       </c>
       <c r="L121" s="5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M121" s="18" t="inlineStr">
         <is>
@@ -12923,7 +12923,7 @@
       </c>
       <c r="N121" s="6" t="inlineStr">
         <is>
-          <t>町データが届くたびに突合対象が増える。とくに成果指標の現状値17項目と令和7年度決算が入ると、素案・算定シート・協議会資料の3系統を同時に照合する必要がある</t>
+          <t>足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。いずれも町データ待ちである。地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
         </is>
       </c>
     </row>
@@ -12940,12 +12940,12 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>11-2</t>
+          <t>11-6</t>
         </is>
       </c>
       <c r="D122" s="6" t="inlineStr">
         <is>
-          <t>図表データ管理台帳の整備と運用</t>
+          <t>ペンディング項目の整理と作業順位の管理</t>
         </is>
       </c>
       <c r="E122" s="5" t="inlineStr">
@@ -12955,12 +12955,12 @@
       </c>
       <c r="F122" s="5" t="inlineStr">
         <is>
-          <t>2026-09</t>
+          <t>2026-10</t>
         </is>
       </c>
       <c r="G122" s="5" t="inlineStr">
         <is>
-          <t>2027-02</t>
+          <t>2027-03</t>
         </is>
       </c>
       <c r="H122" s="16" t="inlineStr">
@@ -12969,16 +12969,16 @@
         </is>
       </c>
       <c r="I122" s="13" t="n">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="J122" s="13" t="n">
-        <v>20</v>
+        <v>3.3</v>
       </c>
       <c r="K122" s="13" t="n">
-        <v>65</v>
+        <v>66.7</v>
       </c>
       <c r="L122" s="5" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M122" s="18" t="inlineStr">
         <is>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="N122" s="6" t="inlineStr">
         <is>
-          <t>足りない図6件のうち、10月4日に要介護度の維持・改善を作成し、残りは2件になった。いずれも町データ待ちである。地域ケア会議の開催回数・検討件数（町の事業実績待ち）と、介護給付適正化の主要3事業の実施状況（町の実施報告待ち）</t>
+          <t>町の回答が届くたびに順位を組み替える。優先1位（基金運用状況調書）の回答が来た時点で、その日の作業を止めて差し替えに回す</t>
         </is>
       </c>
     </row>
@@ -13004,12 +13004,12 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>11-6</t>
+          <t>11-1</t>
         </is>
       </c>
       <c r="D123" s="6" t="inlineStr">
         <is>
-          <t>ペンディング項目の整理と作業順位の管理</t>
+          <t>一次資料との全件突合</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr">
@@ -13019,12 +13019,12 @@
       </c>
       <c r="F123" s="5" t="inlineStr">
         <is>
-          <t>2026-10</t>
+          <t>2026-09</t>
         </is>
       </c>
       <c r="G123" s="5" t="inlineStr">
         <is>
-          <t>2027-03</t>
+          <t>2027-02</t>
         </is>
       </c>
       <c r="H123" s="16" t="inlineStr">
@@ -13033,16 +13033,16 @@
         </is>
       </c>
       <c r="I123" s="13" t="n">
+        <v>90</v>
+      </c>
+      <c r="J123" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="K123" s="13" t="n">
         <v>70</v>
       </c>
-      <c r="J123" s="13" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="K123" s="13" t="n">
-        <v>66.7</v>
-      </c>
       <c r="L123" s="5" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="M123" s="18" t="inlineStr">
         <is>
@@ -13051,7 +13051,7 @@
       </c>
       <c r="N123" s="6" t="inlineStr">
         <is>
-          <t>町の回答が届くたびに順位を組み替える。優先1位（基金運用状況調書）の回答が来た時点で、その日の作業を止めて差し替えに回す</t>
+          <t>町データが届くたびに突合対象が増える。とくに成果指標の現状値17項目と令和7年度決算が入ると、素案・算定シート・協議会資料の3系統を同時に照合する必要がある</t>
         </is>
       </c>
     </row>
@@ -13314,7 +13314,7 @@
     <row r="129">
       <c r="A129" s="19" t="inlineStr">
         <is>
-          <t>高齢者計画　予定進捗率 55.8％　対　実績進捗率 70.7％　乖離 +14.9ポイント　／　おおむね予定どおり 44件／前倒し 25件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
+          <t>高齢者計画　予定進捗率 55.8％　対　実績進捗率 70.9％　乖離 +15.0ポイント　／　おおむね予定どおり 44件／前倒し 25件／遅れ 4件／期限超過（2か月） 2件／期限超過（1か月） 2件</t>
         </is>
       </c>
     </row>
@@ -14249,7 +14249,7 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>check_ono_ichiji.py</t>
+          <t>check_ono_ichiji.py（286件→329件）</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
@@ -14259,17 +14259,17 @@
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>10月8日（木）</t>
-        </is>
-      </c>
-      <c r="H20" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
+          <t>10月7日（水）</t>
+        </is>
+      </c>
+      <c r="H20" s="17" t="inlineStr">
+        <is>
+          <t>完了</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>―</t>
+          <t>10月7日（水）</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>10月9日（金）</t>
+          <t>10月8日（木）</t>
         </is>
       </c>
       <c r="H21" s="12" t="inlineStr">
@@ -14343,7 +14343,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G8"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -14403,16 +14403,16 @@
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>T14</t>
+          <t>T12</t>
         </is>
       </c>
       <c r="D2" s="6" t="inlineStr">
         <is>
-          <t>一次資料との突合の対象を広げる</t>
+          <t>障がい計画の素案の改訂（第2版）</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F2" s="12" t="inlineStr">
         <is>
@@ -14421,7 +14421,7 @@
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>11-1</t>
+          <t>障がい 3-2</t>
         </is>
       </c>
     </row>
@@ -14439,80 +14439,24 @@
         </is>
       </c>
       <c r="E3" s="20" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F3" s="20" t="inlineStr">
         <is>
-          <t>残2.0h</t>
+          <t>残6.0h</t>
         </is>
       </c>
       <c r="G3" s="20" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" s="5" t="inlineStr">
-        <is>
-          <t>10月9日（金）</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="inlineStr">
-        <is>
-          <t>T12</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>障がい計画の素案の改訂（第2版）</t>
-        </is>
-      </c>
-      <c r="E4" s="5" t="n">
-        <v>6</v>
-      </c>
-      <c r="F4" s="12" t="inlineStr">
-        <is>
-          <t>未着手</t>
-        </is>
-      </c>
-      <c r="G4" s="5" t="inlineStr">
-        <is>
-          <t>障がい 3-2</t>
-        </is>
-      </c>
-    </row>
     <row r="5">
-      <c r="A5" s="20" t="inlineStr">
-        <is>
-          <t>10月9日（金）</t>
-        </is>
-      </c>
-      <c r="B5" s="20" t="inlineStr"/>
-      <c r="C5" s="20" t="inlineStr"/>
-      <c r="D5" s="21" t="inlineStr">
-        <is>
-          <t>── 10月9日（金） 計</t>
-        </is>
-      </c>
-      <c r="E5" s="20" t="n">
-        <v>6</v>
-      </c>
-      <c r="F5" s="20" t="inlineStr">
-        <is>
-          <t>残6.0h</t>
-        </is>
-      </c>
-      <c r="G5" s="20" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="11" t="inlineStr">
+      <c r="A5" s="11" t="inlineStr">
         <is>
           <t>※ 10月8日（木）の3件は、いずれも外部の回答を要しません。待ちのある作業を混ぜると、その日の手が止まります。</t>
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="11" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>※ 順番は「手元の資料だけで完結するもの」→「他の作業の前提になるもの」→「後からやると割高になるもの」の順に置いています。</t>
         </is>
@@ -18913,7 +18857,7 @@
         </is>
       </c>
       <c r="H115" s="5" t="n">
-        <v>85</v>
+        <v>90</v>
       </c>
     </row>
     <row r="117">
